--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.78729803886547</v>
+        <v>6.465435931315639</v>
       </c>
       <c r="D2" t="n">
-        <v>39.97605308569246</v>
+        <v>6.496108626425025</v>
       </c>
       <c r="E2" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F2" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.97393236370686</v>
+        <v>4.383264009102366</v>
       </c>
       <c r="D3" t="n">
-        <v>27.00806737169868</v>
+        <v>4.388810947901036</v>
       </c>
       <c r="E3" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F3" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.88995962417947</v>
+        <v>2.907118438929164</v>
       </c>
       <c r="D4" t="n">
-        <v>18.07551221431768</v>
+        <v>2.937270734826623</v>
       </c>
       <c r="E4" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F4" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.30193130916247</v>
+        <v>5.736563837738902</v>
       </c>
       <c r="D5" t="n">
-        <v>35.44642142833693</v>
+        <v>5.760043482104752</v>
       </c>
       <c r="E5" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F5" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.30230296141561</v>
+        <v>8.499124231230036</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21577261077921</v>
+        <v>7.672563049251622</v>
       </c>
       <c r="E6" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F6" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.9772958189857</v>
+        <v>4.058810570585176</v>
       </c>
       <c r="D7" t="n">
-        <v>24.79685331611856</v>
+        <v>4.029488663869267</v>
       </c>
       <c r="E7" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F7" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.93767754280413</v>
+        <v>8.277372600705672</v>
       </c>
       <c r="D8" t="n">
-        <v>49.70068521941635</v>
+        <v>8.076361348155157</v>
       </c>
       <c r="E8" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F8" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.37319363086911</v>
+        <v>6.56064396501623</v>
       </c>
       <c r="D9" t="n">
-        <v>40.55872885062682</v>
+        <v>6.590793438226859</v>
       </c>
       <c r="E9" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F9" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.25004176976671</v>
+        <v>7.028131787587091</v>
       </c>
       <c r="D10" t="n">
-        <v>18.49390982878746</v>
+        <v>3.005260347177962</v>
       </c>
       <c r="E10" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F10" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.63582735229875</v>
+        <v>7.253321944748548</v>
       </c>
       <c r="D11" t="n">
-        <v>14.57737973711325</v>
+        <v>2.368824207280903</v>
       </c>
       <c r="E11" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F11" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.24449877790999</v>
+        <v>7.677231051410374</v>
       </c>
       <c r="D12" t="n">
-        <v>9.949220391159381</v>
+        <v>1.6167483135634</v>
       </c>
       <c r="E12" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F12" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.18464827785964</v>
+        <v>10.26750534515219</v>
       </c>
       <c r="D13" t="n">
-        <v>30.99602457453938</v>
+        <v>5.03685399336265</v>
       </c>
       <c r="E13" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F13" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.38729824568431</v>
+        <v>7.212935964923701</v>
       </c>
       <c r="D14" t="n">
-        <v>19.13765920900464</v>
+        <v>3.109869621463254</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79645975778281</v>
+        <v>1.916924710639707</v>
       </c>
       <c r="F14" t="n">
-        <v>12.33952377585583</v>
+        <v>2.005172613576572</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
